--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9306930693069307</v>
+        <v>0.9532710280373832</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7588652482269503</v>
+        <v>0.795774647887324</v>
       </c>
       <c r="D2">
-        <v>0.265625</v>
+        <v>0.2213740458015267</v>
       </c>
       <c r="E2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
